--- a/artfynd/A 48263-2022 artfynd.xlsx
+++ b/artfynd/A 48263-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 48263-2022 artfynd.xlsx
+++ b/artfynd/A 48263-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -790,6 +790,220 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>123880598</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57506</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Högsby, Högsby, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>542489</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6343087</v>
+      </c>
+      <c r="S3" t="n">
+        <v>15</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Fagerhult</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123881309</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57506</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Högsby, Högsby, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>542479</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6342970</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Fagerhult</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48263-2022 artfynd.xlsx
+++ b/artfynd/A 48263-2022 artfynd.xlsx
@@ -793,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123880598</v>
+        <v>123881309</v>
       </c>
       <c r="B3" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -833,13 +833,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>542489</v>
+        <v>542479</v>
       </c>
       <c r="R3" t="n">
-        <v>6343087</v>
+        <v>6342970</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -900,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123881309</v>
+        <v>123880598</v>
       </c>
       <c r="B4" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -940,13 +940,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>542479</v>
+        <v>542489</v>
       </c>
       <c r="R4" t="n">
-        <v>6342970</v>
+        <v>6343087</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 48263-2022 artfynd.xlsx
+++ b/artfynd/A 48263-2022 artfynd.xlsx
@@ -793,7 +793,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123881309</v>
+        <v>123880598</v>
       </c>
       <c r="B3" t="n">
         <v>57507</v>
@@ -833,13 +833,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>542479</v>
+        <v>542489</v>
       </c>
       <c r="R3" t="n">
-        <v>6342970</v>
+        <v>6343087</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123880598</v>
+        <v>123881309</v>
       </c>
       <c r="B4" t="n">
         <v>57507</v>
@@ -940,13 +940,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>542489</v>
+        <v>542479</v>
       </c>
       <c r="R4" t="n">
-        <v>6343087</v>
+        <v>6342970</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 48263-2022 artfynd.xlsx
+++ b/artfynd/A 48263-2022 artfynd.xlsx
@@ -793,7 +793,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123880598</v>
+        <v>123881309</v>
       </c>
       <c r="B3" t="n">
         <v>57507</v>
@@ -833,13 +833,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>542489</v>
+        <v>542479</v>
       </c>
       <c r="R3" t="n">
-        <v>6343087</v>
+        <v>6342970</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123881309</v>
+        <v>123880598</v>
       </c>
       <c r="B4" t="n">
         <v>57507</v>
@@ -940,13 +940,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>542479</v>
+        <v>542489</v>
       </c>
       <c r="R4" t="n">
-        <v>6342970</v>
+        <v>6343087</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 48263-2022 artfynd.xlsx
+++ b/artfynd/A 48263-2022 artfynd.xlsx
@@ -793,7 +793,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123881309</v>
+        <v>123880598</v>
       </c>
       <c r="B3" t="n">
         <v>57529</v>
@@ -833,13 +833,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>542479</v>
+        <v>542489</v>
       </c>
       <c r="R3" t="n">
-        <v>6342970</v>
+        <v>6343087</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123880598</v>
+        <v>123881309</v>
       </c>
       <c r="B4" t="n">
         <v>57529</v>
@@ -940,13 +940,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>542489</v>
+        <v>542479</v>
       </c>
       <c r="R4" t="n">
-        <v>6343087</v>
+        <v>6342970</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 48263-2022 artfynd.xlsx
+++ b/artfynd/A 48263-2022 artfynd.xlsx
@@ -793,7 +793,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123880598</v>
+        <v>123881309</v>
       </c>
       <c r="B3" t="n">
         <v>57529</v>
@@ -833,13 +833,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>542489</v>
+        <v>542479</v>
       </c>
       <c r="R3" t="n">
-        <v>6343087</v>
+        <v>6342970</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123881309</v>
+        <v>123880598</v>
       </c>
       <c r="B4" t="n">
         <v>57529</v>
@@ -940,13 +940,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>542479</v>
+        <v>542489</v>
       </c>
       <c r="R4" t="n">
-        <v>6342970</v>
+        <v>6343087</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 48263-2022 artfynd.xlsx
+++ b/artfynd/A 48263-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,59 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104913226</v>
+        <v>123880598</v>
       </c>
       <c r="B2" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Högsby, Sm</t>
+          <t>Högsby, Högsby, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>542362.8519435178</v>
+        <v>542489</v>
       </c>
       <c r="R2" t="n">
-        <v>6342895.40791133</v>
+        <v>6343087</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,22 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-12-04</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-12-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,16 +780,11 @@
         <v>123881309</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -900,32 +879,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123880598</v>
+        <v>104913236</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -934,19 +908,20 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Högsby, Högsby, Sm</t>
+          <t>Högsby, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>542489</v>
+        <v>542363</v>
       </c>
       <c r="R4" t="n">
-        <v>6343087</v>
+        <v>6342895</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -970,17 +945,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2022-12-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+          <t>2022-12-04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,6 +974,109 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>104913226</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Högsby, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>542363</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6342895</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Fagerhult</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-12-04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-12-04</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48263-2022 artfynd.xlsx
+++ b/artfynd/A 48263-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123880598</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123881309</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -974,6 +989,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104913236</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1077,8 +1097,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104913226</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>